--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N19_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N19_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.94041033456568</v>
+        <v>5.677816679366924</v>
       </c>
       <c r="D2" t="n">
-        <v>34.98523756314317</v>
+        <v>5.685101104010765</v>
       </c>
       <c r="E2" t="n">
-        <v>14.90748659484371</v>
+        <v>2.422466571662103</v>
       </c>
       <c r="F2" t="n">
-        <v>17.25681075040328</v>
+        <v>2.804231746940534</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.59421409466862</v>
+        <v>5.459059790383652</v>
       </c>
       <c r="D3" t="n">
-        <v>33.53832467511562</v>
+        <v>5.44997775970629</v>
       </c>
       <c r="E3" t="n">
-        <v>14.90748659484371</v>
+        <v>2.422466571662103</v>
       </c>
       <c r="F3" t="n">
-        <v>17.25681075040328</v>
+        <v>2.804231746940534</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>51.63939974662578</v>
+        <v>8.39140245882669</v>
       </c>
       <c r="D4" t="n">
-        <v>51.43438990805927</v>
+        <v>8.358088360059631</v>
       </c>
       <c r="E4" t="n">
-        <v>14.90748659484371</v>
+        <v>2.422466571662103</v>
       </c>
       <c r="F4" t="n">
-        <v>17.25681075040328</v>
+        <v>2.804231746940534</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.081684664425399</v>
+        <v>1.313273757969127</v>
       </c>
       <c r="D5" t="n">
-        <v>7.074965783799698</v>
+        <v>1.149681939867451</v>
       </c>
       <c r="E5" t="n">
-        <v>14.90748659484371</v>
+        <v>2.422466571662103</v>
       </c>
       <c r="F5" t="n">
-        <v>17.25681075040328</v>
+        <v>2.804231746940534</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>29.63251038823788</v>
+        <v>4.815282938088656</v>
       </c>
       <c r="D6" t="n">
-        <v>29.47095278687845</v>
+        <v>4.789029827867749</v>
       </c>
       <c r="E6" t="n">
-        <v>14.90748659484371</v>
+        <v>2.422466571662103</v>
       </c>
       <c r="F6" t="n">
-        <v>17.25681075040328</v>
+        <v>2.804231746940534</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>32.8618374379711</v>
+        <v>5.340048583670304</v>
       </c>
       <c r="D7" t="n">
-        <v>24.31081292347091</v>
+        <v>3.950507100064022</v>
       </c>
       <c r="E7" t="n">
-        <v>14.90748659484371</v>
+        <v>2.422466571662103</v>
       </c>
       <c r="F7" t="n">
-        <v>17.25681075040328</v>
+        <v>2.804231746940534</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.41544083934619</v>
+        <v>5.105009136393757</v>
       </c>
       <c r="D8" t="n">
-        <v>5.987776664819345</v>
+        <v>0.9730137080331436</v>
       </c>
       <c r="E8" t="n">
-        <v>14.90748659484371</v>
+        <v>2.422466571662103</v>
       </c>
       <c r="F8" t="n">
-        <v>17.25681075040328</v>
+        <v>2.804231746940534</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.40509105441762</v>
+        <v>6.240827296342864</v>
       </c>
       <c r="D9" t="n">
-        <v>18.82817038376273</v>
+        <v>3.059577687361444</v>
       </c>
       <c r="E9" t="n">
-        <v>14.90748659484371</v>
+        <v>2.422466571662103</v>
       </c>
       <c r="F9" t="n">
-        <v>17.25681075040328</v>
+        <v>2.804231746940534</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>56.95554930636999</v>
+        <v>9.255276762285124</v>
       </c>
       <c r="D10" t="n">
-        <v>53.48130514488217</v>
+        <v>8.690712086043353</v>
       </c>
       <c r="E10" t="n">
-        <v>14.90748659484371</v>
+        <v>2.422466571662103</v>
       </c>
       <c r="F10" t="n">
-        <v>17.25681075040328</v>
+        <v>2.804231746940534</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>54.65820698851402</v>
+        <v>8.881958635633529</v>
       </c>
       <c r="D11" t="n">
-        <v>54.75970882968561</v>
+        <v>8.898452684823912</v>
       </c>
       <c r="E11" t="n">
-        <v>14.90748659484371</v>
+        <v>2.422466571662103</v>
       </c>
       <c r="F11" t="n">
-        <v>17.25681075040328</v>
+        <v>2.804231746940534</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>12.31021823608285</v>
+        <v>2.000410463363464</v>
       </c>
       <c r="D12" t="n">
-        <v>11.0989045198</v>
+        <v>1.803571984467499</v>
       </c>
       <c r="E12" t="n">
-        <v>14.90748659484371</v>
+        <v>2.422466571662103</v>
       </c>
       <c r="F12" t="n">
-        <v>17.25681075040328</v>
+        <v>2.804231746940534</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
